--- a/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
+++ b/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
@@ -58,25 +58,25 @@
     <t>Tramo 2</t>
   </si>
   <si>
-    <t>Sector E</t>
-  </si>
-  <si>
-    <t>-34.82629827326442, -54.61928315475239</t>
-  </si>
-  <si>
-    <t>Esqueleto</t>
-  </si>
-  <si>
-    <t>Tortuga Cabezona</t>
+    <t>Sector D</t>
+  </si>
+  <si>
+    <t>-34.84066585786591, -54.666520737583255</t>
+  </si>
+  <si>
+    <t>Carcasa</t>
+  </si>
+  <si>
+    <t>pinnipedo</t>
   </si>
   <si>
     <t>ref test</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1O8fg-aa0qQgBg3BP5IoDPVknz0SLhbuO</t>
-  </si>
-  <si>
-    <t>notas test</t>
+    <t>https://drive.google.com/open?id=1Wa7hU-cZPtndJT0jQ5atf94mXkn2VNAn</t>
+  </si>
+  <si>
+    <t>ref notas</t>
   </si>
 </sst>
 </file>
@@ -509,7 +509,7 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="4">
-        <v>46114.474706099536</v>
+        <v>46114.65558759259</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>13</v>
@@ -527,13 +527,13 @@
         <v>46114.0</v>
       </c>
       <c r="G2" s="8">
-        <v>0.4743055555591127</v>
+        <v>0.6548611111065838</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I2" s="5">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>18</v>

--- a/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
+++ b/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -77,6 +77,24 @@
   </si>
   <si>
     <t>ref notas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pablo Rubens Faget </t>
+  </si>
+  <si>
+    <t>34.871647,-54.746436</t>
+  </si>
+  <si>
+    <t>Careta careta</t>
+  </si>
+  <si>
+    <t>Huella Calzado 41 30cm</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1XvkLHYRwc4jGzvlFdtUODOw0iLe06noX, https://drive.google.com/open?id=1eoNEfQS-fVMbJr2xDc6gXMzk7DPViRwm</t>
+  </si>
+  <si>
+    <t>Polo Club ruta 10</t>
   </si>
 </sst>
 </file>
@@ -120,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -149,6 +167,21 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -235,7 +268,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M2" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M3" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="13">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="Relevado por" id="2"/>
@@ -548,415 +581,456 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
-      <c r="E3" s="10"/>
-      <c r="F3" s="11"/>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="10">
+        <v>46115.374011493055</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="13">
+        <v>46115.0</v>
+      </c>
+      <c r="G3" s="14">
+        <v>0.36458333333575865</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="11">
+        <v>4.0</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="4">
-      <c r="E4" s="12"/>
-      <c r="F4" s="11"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5">
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6">
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7">
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16"/>
     </row>
     <row r="8">
-      <c r="E8" s="10"/>
-      <c r="F8" s="11"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="16"/>
     </row>
     <row r="9">
-      <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="16"/>
     </row>
     <row r="10">
-      <c r="E10" s="10"/>
-      <c r="F10" s="11"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11">
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="16"/>
     </row>
     <row r="12">
-      <c r="E12" s="10"/>
-      <c r="F12" s="11"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="16"/>
     </row>
     <row r="13">
-      <c r="E13" s="10"/>
-      <c r="F13" s="11"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16"/>
     </row>
     <row r="14">
-      <c r="E14" s="10"/>
-      <c r="F14" s="11"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="16"/>
     </row>
     <row r="15">
-      <c r="E15" s="10"/>
-      <c r="F15" s="11"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="16"/>
     </row>
     <row r="16">
-      <c r="E16" s="10"/>
-      <c r="F16" s="11"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16"/>
     </row>
     <row r="17">
-      <c r="E17" s="10"/>
-      <c r="F17" s="11"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18">
-      <c r="E18" s="10"/>
-      <c r="F18" s="11"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="19">
-      <c r="E19" s="10"/>
-      <c r="F19" s="11"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="16"/>
     </row>
     <row r="20">
-      <c r="E20" s="10"/>
-      <c r="F20" s="11"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="16"/>
     </row>
     <row r="21">
-      <c r="E21" s="10"/>
-      <c r="F21" s="11"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22">
-      <c r="E22" s="10"/>
-      <c r="F22" s="11"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23">
-      <c r="E23" s="10"/>
-      <c r="F23" s="11"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
     </row>
     <row r="24">
-      <c r="E24" s="10"/>
-      <c r="F24" s="11"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16"/>
     </row>
     <row r="25">
-      <c r="E25" s="10"/>
-      <c r="F25" s="11"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="16"/>
     </row>
     <row r="26">
-      <c r="E26" s="10"/>
-      <c r="F26" s="11"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27">
-      <c r="E27" s="10"/>
-      <c r="F27" s="11"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="16"/>
     </row>
     <row r="28">
-      <c r="E28" s="10"/>
-      <c r="F28" s="11"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="16"/>
     </row>
     <row r="29">
-      <c r="E29" s="10"/>
-      <c r="F29" s="11"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="30">
-      <c r="E30" s="10"/>
-      <c r="F30" s="11"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="16"/>
     </row>
     <row r="31">
-      <c r="E31" s="10"/>
-      <c r="F31" s="11"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16"/>
     </row>
     <row r="32">
-      <c r="E32" s="10"/>
-      <c r="F32" s="11"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="16"/>
     </row>
     <row r="33">
-      <c r="E33" s="10"/>
-      <c r="F33" s="11"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="16"/>
     </row>
     <row r="34">
-      <c r="E34" s="10"/>
-      <c r="F34" s="11"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="16"/>
     </row>
     <row r="35">
-      <c r="E35" s="10"/>
-      <c r="F35" s="11"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="16"/>
     </row>
     <row r="36">
-      <c r="E36" s="10"/>
-      <c r="F36" s="11"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="16"/>
     </row>
     <row r="37">
-      <c r="E37" s="10"/>
-      <c r="F37" s="11"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="16"/>
     </row>
     <row r="38">
-      <c r="E38" s="10"/>
-      <c r="F38" s="11"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="16"/>
     </row>
     <row r="39">
-      <c r="E39" s="10"/>
-      <c r="F39" s="11"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="16"/>
     </row>
     <row r="40">
-      <c r="E40" s="10"/>
-      <c r="F40" s="11"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="16"/>
     </row>
     <row r="41">
-      <c r="E41" s="10"/>
-      <c r="F41" s="11"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="16"/>
     </row>
     <row r="42">
-      <c r="E42" s="10"/>
-      <c r="F42" s="11"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="16"/>
     </row>
     <row r="43">
-      <c r="E43" s="10"/>
-      <c r="F43" s="11"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="16"/>
     </row>
     <row r="44">
-      <c r="E44" s="10"/>
-      <c r="F44" s="11"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="16"/>
     </row>
     <row r="45">
-      <c r="E45" s="10"/>
-      <c r="F45" s="11"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="16"/>
     </row>
     <row r="46">
-      <c r="E46" s="10"/>
-      <c r="F46" s="11"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="16"/>
     </row>
     <row r="47">
-      <c r="E47" s="10"/>
-      <c r="F47" s="11"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="16"/>
     </row>
     <row r="48">
-      <c r="E48" s="10"/>
-      <c r="F48" s="11"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="16"/>
     </row>
     <row r="49">
-      <c r="E49" s="10"/>
-      <c r="F49" s="11"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="16"/>
     </row>
     <row r="50">
-      <c r="E50" s="10"/>
-      <c r="F50" s="11"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="16"/>
     </row>
     <row r="51">
-      <c r="E51" s="10"/>
-      <c r="F51" s="11"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="16"/>
     </row>
     <row r="52">
-      <c r="E52" s="10"/>
-      <c r="F52" s="11"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="16"/>
     </row>
     <row r="53">
-      <c r="E53" s="10"/>
-      <c r="F53" s="11"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="16"/>
     </row>
     <row r="54">
-      <c r="E54" s="10"/>
-      <c r="F54" s="11"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
     </row>
     <row r="55">
-      <c r="E55" s="10"/>
-      <c r="F55" s="11"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16"/>
     </row>
     <row r="56">
-      <c r="E56" s="10"/>
-      <c r="F56" s="11"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="16"/>
     </row>
     <row r="57">
-      <c r="E57" s="10"/>
-      <c r="F57" s="11"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="16"/>
     </row>
     <row r="58">
-      <c r="E58" s="10"/>
-      <c r="F58" s="11"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="16"/>
     </row>
     <row r="59">
-      <c r="E59" s="10"/>
-      <c r="F59" s="11"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="16"/>
     </row>
     <row r="60">
-      <c r="E60" s="10"/>
-      <c r="F60" s="11"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="16"/>
     </row>
     <row r="61">
-      <c r="E61" s="10"/>
-      <c r="F61" s="11"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="16"/>
     </row>
     <row r="62">
-      <c r="E62" s="10"/>
-      <c r="F62" s="11"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="16"/>
     </row>
     <row r="63">
-      <c r="E63" s="10"/>
-      <c r="F63" s="11"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="16"/>
     </row>
     <row r="64">
-      <c r="E64" s="10"/>
-      <c r="F64" s="11"/>
+      <c r="E64" s="15"/>
+      <c r="F64" s="16"/>
     </row>
     <row r="65">
-      <c r="E65" s="10"/>
-      <c r="F65" s="11"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="16"/>
     </row>
     <row r="66">
-      <c r="E66" s="10"/>
-      <c r="F66" s="11"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="16"/>
     </row>
     <row r="67">
-      <c r="E67" s="10"/>
-      <c r="F67" s="11"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="16"/>
     </row>
     <row r="68">
-      <c r="E68" s="10"/>
-      <c r="F68" s="11"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="16"/>
     </row>
     <row r="69">
-      <c r="E69" s="10"/>
-      <c r="F69" s="11"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="16"/>
     </row>
     <row r="70">
-      <c r="E70" s="10"/>
-      <c r="F70" s="11"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="16"/>
     </row>
     <row r="71">
-      <c r="E71" s="10"/>
-      <c r="F71" s="11"/>
+      <c r="E71" s="15"/>
+      <c r="F71" s="16"/>
     </row>
     <row r="72">
-      <c r="E72" s="10"/>
-      <c r="F72" s="11"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="16"/>
     </row>
     <row r="73">
-      <c r="E73" s="10"/>
-      <c r="F73" s="11"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="16"/>
     </row>
     <row r="74">
-      <c r="E74" s="10"/>
-      <c r="F74" s="11"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="16"/>
     </row>
     <row r="75">
-      <c r="E75" s="10"/>
-      <c r="F75" s="11"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="16"/>
     </row>
     <row r="76">
-      <c r="E76" s="10"/>
-      <c r="F76" s="11"/>
+      <c r="E76" s="15"/>
+      <c r="F76" s="16"/>
     </row>
     <row r="77">
-      <c r="E77" s="10"/>
-      <c r="F77" s="11"/>
+      <c r="E77" s="15"/>
+      <c r="F77" s="16"/>
     </row>
     <row r="78">
-      <c r="E78" s="10"/>
-      <c r="F78" s="11"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="16"/>
     </row>
     <row r="79">
-      <c r="E79" s="10"/>
-      <c r="F79" s="11"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="16"/>
     </row>
     <row r="80">
-      <c r="E80" s="10"/>
-      <c r="F80" s="11"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="16"/>
     </row>
     <row r="81">
-      <c r="E81" s="10"/>
-      <c r="F81" s="11"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="16"/>
     </row>
     <row r="82">
-      <c r="E82" s="10"/>
-      <c r="F82" s="11"/>
+      <c r="E82" s="15"/>
+      <c r="F82" s="16"/>
     </row>
     <row r="83">
-      <c r="E83" s="10"/>
-      <c r="F83" s="11"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="16"/>
     </row>
     <row r="84">
-      <c r="E84" s="10"/>
-      <c r="F84" s="11"/>
+      <c r="E84" s="15"/>
+      <c r="F84" s="16"/>
     </row>
     <row r="85">
-      <c r="E85" s="10"/>
-      <c r="F85" s="11"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="16"/>
     </row>
     <row r="86">
-      <c r="E86" s="10"/>
-      <c r="F86" s="11"/>
+      <c r="E86" s="15"/>
+      <c r="F86" s="16"/>
     </row>
     <row r="87">
-      <c r="E87" s="10"/>
-      <c r="F87" s="11"/>
+      <c r="E87" s="15"/>
+      <c r="F87" s="16"/>
     </row>
     <row r="88">
-      <c r="E88" s="10"/>
-      <c r="F88" s="11"/>
+      <c r="E88" s="15"/>
+      <c r="F88" s="16"/>
     </row>
     <row r="89">
-      <c r="E89" s="10"/>
-      <c r="F89" s="11"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="16"/>
     </row>
     <row r="90">
-      <c r="E90" s="10"/>
-      <c r="F90" s="11"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="16"/>
     </row>
     <row r="91">
-      <c r="E91" s="10"/>
-      <c r="F91" s="11"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="16"/>
     </row>
     <row r="92">
-      <c r="E92" s="10"/>
-      <c r="F92" s="11"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="16"/>
     </row>
     <row r="93">
-      <c r="E93" s="10"/>
-      <c r="F93" s="11"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="16"/>
     </row>
     <row r="94">
-      <c r="E94" s="10"/>
-      <c r="F94" s="11"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="16"/>
     </row>
     <row r="95">
-      <c r="E95" s="10"/>
-      <c r="F95" s="11"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="16"/>
     </row>
     <row r="96">
-      <c r="E96" s="10"/>
-      <c r="F96" s="11"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="16"/>
     </row>
     <row r="97">
-      <c r="E97" s="10"/>
-      <c r="F97" s="11"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="16"/>
     </row>
     <row r="98">
-      <c r="E98" s="10"/>
-      <c r="F98" s="11"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="16"/>
     </row>
     <row r="99">
-      <c r="E99" s="10"/>
-      <c r="F99" s="11"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="16"/>
     </row>
     <row r="100">
-      <c r="E100" s="10"/>
-      <c r="F100" s="11"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="16"/>
     </row>
     <row r="101">
-      <c r="E101" s="10"/>
-      <c r="F101" s="11"/>
+      <c r="E101" s="15"/>
+      <c r="F101" s="16"/>
     </row>
     <row r="102">
-      <c r="E102" s="10"/>
-      <c r="F102" s="11"/>
+      <c r="E102" s="15"/>
+      <c r="F102" s="16"/>
+    </row>
+    <row r="103">
+      <c r="E103" s="15"/>
+      <c r="F103" s="16"/>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G3">
       <formula1>OR(TIMEVALUE(TEXT(G2, "hh:mm:ss"))=G2, AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F3">
       <formula1>OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="E2"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E3"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="L2"/>

--- a/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
+++ b/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -52,7 +52,7 @@
     <t>Notas</t>
   </si>
   <si>
-    <t>German</t>
+    <t xml:space="preserve">Pablo Rubens Faget </t>
   </si>
   <si>
     <t>Tramo 2</t>
@@ -61,31 +61,13 @@
     <t>Sector D</t>
   </si>
   <si>
-    <t>-34.84066585786591, -54.666520737583255</t>
+    <t>-34.871647,-54.746436</t>
   </si>
   <si>
     <t>Carcasa</t>
   </si>
   <si>
-    <t>pinnipedo</t>
-  </si>
-  <si>
-    <t>ref test</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1Wa7hU-cZPtndJT0jQ5atf94mXkn2VNAn</t>
-  </si>
-  <si>
-    <t>ref notas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pablo Rubens Faget </t>
-  </si>
-  <si>
-    <t>34.871647,-54.746436</t>
-  </si>
-  <si>
-    <t>Careta careta</t>
+    <t>Caretta caretta</t>
   </si>
   <si>
     <t>Huella Calzado 41 30cm</t>
@@ -95,6 +77,78 @@
   </si>
   <si>
     <t>Polo Club ruta 10</t>
+  </si>
+  <si>
+    <t>Sector E</t>
+  </si>
+  <si>
+    <t>-34.8009310, -54.5647690</t>
+  </si>
+  <si>
+    <t>A definir ave</t>
+  </si>
+  <si>
+    <t>Marcador verde</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=10JR0Fam1_TrA47lL-0SlKqHit_CNqclk, https://drive.google.com/open?id=1ANLKItSbaZp4uDBMmXzXq24N42pUHwrJ</t>
+  </si>
+  <si>
+    <t>Viento sur</t>
+  </si>
+  <si>
+    <t>-34.8029920, -54.5692630</t>
+  </si>
+  <si>
+    <t>Sp pinnipedo</t>
+  </si>
+  <si>
+    <t>Marcador y cinta metrica 90cm</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1g7l_NThfd8_pSRL5a_cJNWhdab9CJw2M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> tormenta disminuyendo viento sur</t>
+  </si>
+  <si>
+    <t>-34.7989230, -54.5603620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70cm marcador verde y cinta métrica </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=16WHPfA_RjF_D75S16xWJr4TLECbaeXfm, https://drive.google.com/open?id=1IDLORMrSP9soNDjsWhaxPzgg6UM8V92I</t>
+  </si>
+  <si>
+    <t>Viento sur. Tormenta amainando</t>
+  </si>
+  <si>
+    <t>-34.7964350, -54.5554860</t>
+  </si>
+  <si>
+    <t>Esqueleto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varios tortugas y pinnipedos </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1d1CQ1PkLS5PXq7ggO_i2bdSZumIQIHiL</t>
+  </si>
+  <si>
+    <t>Grupo de carcasas mezclados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sp pinnipedo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cinta metrica y macador verde </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=118V5bEWzqmw_NLVFayTrq56gv80mqORt</t>
+  </si>
+  <si>
+    <t>Grupo de animales</t>
   </si>
 </sst>
 </file>
@@ -138,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -167,21 +221,6 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -268,7 +307,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M3" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M7" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="13">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="Relevado por" id="2"/>
@@ -542,7 +581,7 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="4">
-        <v>46114.65558759259</v>
+        <v>46115.374011493055</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>13</v>
@@ -557,16 +596,16 @@
         <v>16</v>
       </c>
       <c r="F2" s="7">
-        <v>46114.0</v>
+        <v>46115.0</v>
       </c>
       <c r="G2" s="8">
-        <v>0.6548611111065838</v>
+        <v>0.36458333333575865</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I2" s="5">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>18</v>
@@ -574,7 +613,7 @@
       <c r="K2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="5" t="s">
         <v>20</v>
       </c>
       <c r="M2" s="5" t="s">
@@ -582,462 +621,628 @@
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="10">
-        <v>46115.374011493055</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="A3" s="4">
+        <v>46117.36702034722</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="E3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="7">
+        <v>46117.0</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0.36458333333575865</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="4">
+        <v>46117.37743608796</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="13">
-        <v>46115.0</v>
-      </c>
-      <c r="G3" s="14">
-        <v>0.36458333333575865</v>
-      </c>
-      <c r="H3" s="11" t="s">
+      <c r="D4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="7">
+        <v>46117.0</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.37847222221898846</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I4" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="4">
+        <v>46117.39656770833</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="7">
+        <v>46117.0</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0.39583333333575865</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="5">
         <v>4.0</v>
       </c>
-      <c r="J3" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="11" t="s">
+      <c r="J5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="4">
+        <v>46117.42705261574</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="7">
+        <v>46117.0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0.41666666666424135</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="E4" s="15"/>
-      <c r="F4" s="16"/>
-    </row>
-    <row r="5">
-      <c r="E5" s="17"/>
-      <c r="F5" s="16"/>
-    </row>
-    <row r="6">
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
-    </row>
-    <row r="7">
-      <c r="E7" s="15"/>
-      <c r="F7" s="16"/>
+      <c r="L6" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="4">
+        <v>46117.664241990744</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="7">
+        <v>46117.0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0.4131944444452529</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="8">
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="11"/>
     </row>
     <row r="9">
-      <c r="E9" s="15"/>
-      <c r="F9" s="16"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10">
-      <c r="E10" s="15"/>
-      <c r="F10" s="16"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="11">
-      <c r="E11" s="15"/>
-      <c r="F11" s="16"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12">
-      <c r="E12" s="15"/>
-      <c r="F12" s="16"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="11"/>
     </row>
     <row r="13">
-      <c r="E13" s="15"/>
-      <c r="F13" s="16"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14">
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15">
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16">
-      <c r="E16" s="15"/>
-      <c r="F16" s="16"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="11"/>
     </row>
     <row r="17">
-      <c r="E17" s="15"/>
-      <c r="F17" s="16"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18">
-      <c r="E18" s="15"/>
-      <c r="F18" s="16"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="11"/>
     </row>
     <row r="19">
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20">
-      <c r="E20" s="15"/>
-      <c r="F20" s="16"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="11"/>
     </row>
     <row r="21">
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="22">
-      <c r="E22" s="15"/>
-      <c r="F22" s="16"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="11"/>
     </row>
     <row r="23">
-      <c r="E23" s="15"/>
-      <c r="F23" s="16"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24">
-      <c r="E24" s="15"/>
-      <c r="F24" s="16"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="25">
-      <c r="E25" s="15"/>
-      <c r="F25" s="16"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="11"/>
     </row>
     <row r="26">
-      <c r="E26" s="15"/>
-      <c r="F26" s="16"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="27">
-      <c r="E27" s="15"/>
-      <c r="F27" s="16"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="11"/>
     </row>
     <row r="28">
-      <c r="E28" s="15"/>
-      <c r="F28" s="16"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="11"/>
     </row>
     <row r="29">
-      <c r="E29" s="15"/>
-      <c r="F29" s="16"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="11"/>
     </row>
     <row r="30">
-      <c r="E30" s="15"/>
-      <c r="F30" s="16"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="11"/>
     </row>
     <row r="31">
-      <c r="E31" s="15"/>
-      <c r="F31" s="16"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="11"/>
     </row>
     <row r="32">
-      <c r="E32" s="15"/>
-      <c r="F32" s="16"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="11"/>
     </row>
     <row r="33">
-      <c r="E33" s="15"/>
-      <c r="F33" s="16"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="11"/>
     </row>
     <row r="34">
-      <c r="E34" s="15"/>
-      <c r="F34" s="16"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="11"/>
     </row>
     <row r="35">
-      <c r="E35" s="15"/>
-      <c r="F35" s="16"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="11"/>
     </row>
     <row r="36">
-      <c r="E36" s="15"/>
-      <c r="F36" s="16"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="11"/>
     </row>
     <row r="37">
-      <c r="E37" s="15"/>
-      <c r="F37" s="16"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="11"/>
     </row>
     <row r="38">
-      <c r="E38" s="15"/>
-      <c r="F38" s="16"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="11"/>
     </row>
     <row r="39">
-      <c r="E39" s="15"/>
-      <c r="F39" s="16"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="11"/>
     </row>
     <row r="40">
-      <c r="E40" s="15"/>
-      <c r="F40" s="16"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="11"/>
     </row>
     <row r="41">
-      <c r="E41" s="15"/>
-      <c r="F41" s="16"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="11"/>
     </row>
     <row r="42">
-      <c r="E42" s="15"/>
-      <c r="F42" s="16"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="11"/>
     </row>
     <row r="43">
-      <c r="E43" s="15"/>
-      <c r="F43" s="16"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="11"/>
     </row>
     <row r="44">
-      <c r="E44" s="15"/>
-      <c r="F44" s="16"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="11"/>
     </row>
     <row r="45">
-      <c r="E45" s="15"/>
-      <c r="F45" s="16"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="11"/>
     </row>
     <row r="46">
-      <c r="E46" s="15"/>
-      <c r="F46" s="16"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="11"/>
     </row>
     <row r="47">
-      <c r="E47" s="15"/>
-      <c r="F47" s="16"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="11"/>
     </row>
     <row r="48">
-      <c r="E48" s="15"/>
-      <c r="F48" s="16"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="11"/>
     </row>
     <row r="49">
-      <c r="E49" s="15"/>
-      <c r="F49" s="16"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="11"/>
     </row>
     <row r="50">
-      <c r="E50" s="15"/>
-      <c r="F50" s="16"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="11"/>
     </row>
     <row r="51">
-      <c r="E51" s="15"/>
-      <c r="F51" s="16"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="11"/>
     </row>
     <row r="52">
-      <c r="E52" s="15"/>
-      <c r="F52" s="16"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="11"/>
     </row>
     <row r="53">
-      <c r="E53" s="15"/>
-      <c r="F53" s="16"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="11"/>
     </row>
     <row r="54">
-      <c r="E54" s="15"/>
-      <c r="F54" s="16"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="11"/>
     </row>
     <row r="55">
-      <c r="E55" s="15"/>
-      <c r="F55" s="16"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="11"/>
     </row>
     <row r="56">
-      <c r="E56" s="15"/>
-      <c r="F56" s="16"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="11"/>
     </row>
     <row r="57">
-      <c r="E57" s="15"/>
-      <c r="F57" s="16"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="11"/>
     </row>
     <row r="58">
-      <c r="E58" s="15"/>
-      <c r="F58" s="16"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="11"/>
     </row>
     <row r="59">
-      <c r="E59" s="15"/>
-      <c r="F59" s="16"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="11"/>
     </row>
     <row r="60">
-      <c r="E60" s="15"/>
-      <c r="F60" s="16"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="11"/>
     </row>
     <row r="61">
-      <c r="E61" s="15"/>
-      <c r="F61" s="16"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="11"/>
     </row>
     <row r="62">
-      <c r="E62" s="15"/>
-      <c r="F62" s="16"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="11"/>
     </row>
     <row r="63">
-      <c r="E63" s="15"/>
-      <c r="F63" s="16"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="11"/>
     </row>
     <row r="64">
-      <c r="E64" s="15"/>
-      <c r="F64" s="16"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="11"/>
     </row>
     <row r="65">
-      <c r="E65" s="15"/>
-      <c r="F65" s="16"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="11"/>
     </row>
     <row r="66">
-      <c r="E66" s="15"/>
-      <c r="F66" s="16"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="11"/>
     </row>
     <row r="67">
-      <c r="E67" s="15"/>
-      <c r="F67" s="16"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="11"/>
     </row>
     <row r="68">
-      <c r="E68" s="15"/>
-      <c r="F68" s="16"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="11"/>
     </row>
     <row r="69">
-      <c r="E69" s="15"/>
-      <c r="F69" s="16"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="11"/>
     </row>
     <row r="70">
-      <c r="E70" s="15"/>
-      <c r="F70" s="16"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="11"/>
     </row>
     <row r="71">
-      <c r="E71" s="15"/>
-      <c r="F71" s="16"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="11"/>
     </row>
     <row r="72">
-      <c r="E72" s="15"/>
-      <c r="F72" s="16"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="11"/>
     </row>
     <row r="73">
-      <c r="E73" s="15"/>
-      <c r="F73" s="16"/>
+      <c r="E73" s="10"/>
+      <c r="F73" s="11"/>
     </row>
     <row r="74">
-      <c r="E74" s="15"/>
-      <c r="F74" s="16"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="11"/>
     </row>
     <row r="75">
-      <c r="E75" s="15"/>
-      <c r="F75" s="16"/>
+      <c r="E75" s="10"/>
+      <c r="F75" s="11"/>
     </row>
     <row r="76">
-      <c r="E76" s="15"/>
-      <c r="F76" s="16"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="11"/>
     </row>
     <row r="77">
-      <c r="E77" s="15"/>
-      <c r="F77" s="16"/>
+      <c r="E77" s="10"/>
+      <c r="F77" s="11"/>
     </row>
     <row r="78">
-      <c r="E78" s="15"/>
-      <c r="F78" s="16"/>
+      <c r="E78" s="10"/>
+      <c r="F78" s="11"/>
     </row>
     <row r="79">
-      <c r="E79" s="15"/>
-      <c r="F79" s="16"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="11"/>
     </row>
     <row r="80">
-      <c r="E80" s="15"/>
-      <c r="F80" s="16"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="11"/>
     </row>
     <row r="81">
-      <c r="E81" s="15"/>
-      <c r="F81" s="16"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="11"/>
     </row>
     <row r="82">
-      <c r="E82" s="15"/>
-      <c r="F82" s="16"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="11"/>
     </row>
     <row r="83">
-      <c r="E83" s="15"/>
-      <c r="F83" s="16"/>
+      <c r="E83" s="10"/>
+      <c r="F83" s="11"/>
     </row>
     <row r="84">
-      <c r="E84" s="15"/>
-      <c r="F84" s="16"/>
+      <c r="E84" s="10"/>
+      <c r="F84" s="11"/>
     </row>
     <row r="85">
-      <c r="E85" s="15"/>
-      <c r="F85" s="16"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="11"/>
     </row>
     <row r="86">
-      <c r="E86" s="15"/>
-      <c r="F86" s="16"/>
+      <c r="E86" s="10"/>
+      <c r="F86" s="11"/>
     </row>
     <row r="87">
-      <c r="E87" s="15"/>
-      <c r="F87" s="16"/>
+      <c r="E87" s="10"/>
+      <c r="F87" s="11"/>
     </row>
     <row r="88">
-      <c r="E88" s="15"/>
-      <c r="F88" s="16"/>
+      <c r="E88" s="10"/>
+      <c r="F88" s="11"/>
     </row>
     <row r="89">
-      <c r="E89" s="15"/>
-      <c r="F89" s="16"/>
+      <c r="E89" s="10"/>
+      <c r="F89" s="11"/>
     </row>
     <row r="90">
-      <c r="E90" s="15"/>
-      <c r="F90" s="16"/>
+      <c r="E90" s="10"/>
+      <c r="F90" s="11"/>
     </row>
     <row r="91">
-      <c r="E91" s="15"/>
-      <c r="F91" s="16"/>
+      <c r="E91" s="10"/>
+      <c r="F91" s="11"/>
     </row>
     <row r="92">
-      <c r="E92" s="15"/>
-      <c r="F92" s="16"/>
+      <c r="E92" s="10"/>
+      <c r="F92" s="11"/>
     </row>
     <row r="93">
-      <c r="E93" s="15"/>
-      <c r="F93" s="16"/>
+      <c r="E93" s="10"/>
+      <c r="F93" s="11"/>
     </row>
     <row r="94">
-      <c r="E94" s="15"/>
-      <c r="F94" s="16"/>
+      <c r="E94" s="10"/>
+      <c r="F94" s="11"/>
     </row>
     <row r="95">
-      <c r="E95" s="15"/>
-      <c r="F95" s="16"/>
+      <c r="E95" s="10"/>
+      <c r="F95" s="11"/>
     </row>
     <row r="96">
-      <c r="E96" s="15"/>
-      <c r="F96" s="16"/>
+      <c r="E96" s="10"/>
+      <c r="F96" s="11"/>
     </row>
     <row r="97">
-      <c r="E97" s="15"/>
-      <c r="F97" s="16"/>
+      <c r="E97" s="10"/>
+      <c r="F97" s="11"/>
     </row>
     <row r="98">
-      <c r="E98" s="15"/>
-      <c r="F98" s="16"/>
+      <c r="E98" s="10"/>
+      <c r="F98" s="11"/>
     </row>
     <row r="99">
-      <c r="E99" s="15"/>
-      <c r="F99" s="16"/>
+      <c r="E99" s="10"/>
+      <c r="F99" s="11"/>
     </row>
     <row r="100">
-      <c r="E100" s="15"/>
-      <c r="F100" s="16"/>
+      <c r="E100" s="10"/>
+      <c r="F100" s="11"/>
     </row>
     <row r="101">
-      <c r="E101" s="15"/>
-      <c r="F101" s="16"/>
+      <c r="E101" s="10"/>
+      <c r="F101" s="11"/>
     </row>
     <row r="102">
-      <c r="E102" s="15"/>
-      <c r="F102" s="16"/>
+      <c r="E102" s="10"/>
+      <c r="F102" s="11"/>
     </row>
     <row r="103">
-      <c r="E103" s="15"/>
-      <c r="F103" s="16"/>
+      <c r="E103" s="10"/>
+      <c r="F103" s="11"/>
+    </row>
+    <row r="104">
+      <c r="E104" s="10"/>
+      <c r="F104" s="11"/>
+    </row>
+    <row r="105">
+      <c r="E105" s="10"/>
+      <c r="F105" s="11"/>
+    </row>
+    <row r="106">
+      <c r="E106" s="10"/>
+      <c r="F106" s="11"/>
+    </row>
+    <row r="107">
+      <c r="E107" s="10"/>
+      <c r="F107" s="11"/>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G3">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G7">
       <formula1>OR(TIMEVALUE(TEXT(G2, "hh:mm:ss"))=G2, AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F3">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F7">
       <formula1>OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E3"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E7"/>
   </dataValidations>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="L2"/>
+    <hyperlink r:id="rId1" ref="L4"/>
+    <hyperlink r:id="rId2" ref="L6"/>
+    <hyperlink r:id="rId3" ref="L7"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
+++ b/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="75">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -149,6 +149,103 @@
   </si>
   <si>
     <t>Grupo de animales</t>
+  </si>
+  <si>
+    <t>-34.7863310, -54.5336580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sp pinnípedo </t>
+  </si>
+  <si>
+    <t>Viento Este</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1vevCeL4rmD6M_yLk4DtF3OWyCkLny3fr</t>
+  </si>
+  <si>
+    <t>Sin</t>
+  </si>
+  <si>
+    <t>-34.7821180, -54.5243910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cinta métrica y marcador verde </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1xhAVgHypckATfBmRjtDombwrDJH9Xsfs, https://drive.google.com/open?id=1v8bMg1Y3HaFhxTFcLVquOrToMhCUIUdU</t>
+  </si>
+  <si>
+    <t>Viento del Este amainando</t>
+  </si>
+  <si>
+    <t>-34.7816800, -54.5238830</t>
+  </si>
+  <si>
+    <t>Sp ave</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/open?id=1P_4i0PVNC1Cup8U082cJlGUXFqu-a8sc</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>, https://drive.google.com/open?id=102yaPneY7kHJvjZjMpj_GX_Z-VK4yRed, https://drive.google.com/open?id=1XU45Ykh3CEeTox5jLrn38H9qfxU-5O-a</t>
+    </r>
+  </si>
+  <si>
+    <t>Pablo Rubens Faget</t>
+  </si>
+  <si>
+    <t>-34.847414, -54.690754</t>
+  </si>
+  <si>
+    <t>Marcador verde y Cinta metrica</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=10qSZwpUbtKjcPB0ncw_Ir9_ZTZmDZw00</t>
+  </si>
+  <si>
+    <t>dia post tormenta viento sur</t>
+  </si>
+  <si>
+    <t>-34.7665430, -54.4907010</t>
+  </si>
+  <si>
+    <t>PIE 41</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1eq1x9mCokYUKTSwaHgLV_Yabl9a5Bfdf</t>
+  </si>
+  <si>
+    <t>-34.7732190, -54.5051470</t>
+  </si>
+  <si>
+    <t>Reptil tortuga</t>
+  </si>
+  <si>
+    <t>Pie 41</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1sV-5DqCQEK80MyqLKV8bcTFju4jB4H_z, https://drive.google.com/open?id=1SRubYqeCU6Q9cxvsY72osePPAmO0eCYb, https://drive.google.com/open?id=1RIbxjbfsMGUKNpP6HoFg4knJeki_2td_</t>
+  </si>
+  <si>
+    <t>-34.8453770, -54.6316270</t>
+  </si>
+  <si>
+    <t>Indefinida sp cetáceo</t>
+  </si>
+  <si>
+    <t>Chancleta 41</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Of4-LvHG0zctnMODvdDQN9NsEKs6pGWg, https://drive.google.com/open?id=10iVjgs8drQah_isOasUMR2rJDYCiIZ_J, https://drive.google.com/open?id=1PvMiTyYgSZu8oYwV1X_Ab2geYVC7HUmq, https://drive.google.com/open?id=1HnGbj3qBkB90AEfi-1Gh0Nden4MDbw2n, https://drive.google.com/open?id=12jS5LvPt8DJTG4sECIqzWE15pkFfwk_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fue retirado por cuadrilla de limpieza de playas de José Ignacio </t>
   </si>
 </sst>
 </file>
@@ -160,7 +257,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="H:mm:ss"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -175,6 +272,16 @@
     <font>
       <u/>
       <color rgb="FF0000FF"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF434343"/>
       <name val="Roboto"/>
     </font>
   </fonts>
@@ -192,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -221,6 +328,12 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -307,7 +420,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M7" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M14" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="13">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="Relevado por" id="2"/>
@@ -825,424 +938,712 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8">
-      <c r="E8" s="10"/>
-      <c r="F8" s="11"/>
-    </row>
-    <row r="9">
-      <c r="E9" s="12"/>
-      <c r="F9" s="11"/>
-    </row>
-    <row r="10">
-      <c r="E10" s="10"/>
-      <c r="F10" s="11"/>
-    </row>
-    <row r="11">
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
-    </row>
-    <row r="12">
-      <c r="E12" s="10"/>
-      <c r="F12" s="11"/>
-    </row>
-    <row r="13">
-      <c r="E13" s="10"/>
-      <c r="F13" s="11"/>
-    </row>
-    <row r="14">
-      <c r="E14" s="10"/>
-      <c r="F14" s="11"/>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="4">
+        <v>46118.401578159726</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="7">
+        <v>46118.0</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0.3993055555547471</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="4">
+        <v>46118.41902320602</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="7">
+        <v>46118.0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.41666666666424135</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="4">
+        <v>46118.43030375</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="7">
+        <v>46118.0</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0.4243055555562023</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="4">
+        <v>46118.633984988424</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="7">
+        <v>46118.0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0.5555555555547471</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="4">
+        <v>46119.7058852662</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="7">
+        <v>46102.0</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.33333333333575865</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="4">
+        <v>46119.70861369213</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="7">
+        <v>46102.0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.40277777778101154</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="4">
+        <v>46119.71363675926</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="7">
+        <v>46103.0</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0.3819444444452529</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="15">
-      <c r="E15" s="10"/>
-      <c r="F15" s="11"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="13"/>
     </row>
     <row r="16">
-      <c r="E16" s="10"/>
-      <c r="F16" s="11"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="13"/>
     </row>
     <row r="17">
-      <c r="E17" s="10"/>
-      <c r="F17" s="11"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
     </row>
     <row r="18">
-      <c r="E18" s="10"/>
-      <c r="F18" s="11"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="13"/>
     </row>
     <row r="19">
-      <c r="E19" s="10"/>
-      <c r="F19" s="11"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="13"/>
     </row>
     <row r="20">
-      <c r="E20" s="10"/>
-      <c r="F20" s="11"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="13"/>
     </row>
     <row r="21">
-      <c r="E21" s="10"/>
-      <c r="F21" s="11"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="13"/>
     </row>
     <row r="22">
-      <c r="E22" s="10"/>
-      <c r="F22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="13"/>
     </row>
     <row r="23">
-      <c r="E23" s="10"/>
-      <c r="F23" s="11"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="13"/>
     </row>
     <row r="24">
-      <c r="E24" s="10"/>
-      <c r="F24" s="11"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="13"/>
     </row>
     <row r="25">
-      <c r="E25" s="10"/>
-      <c r="F25" s="11"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="13"/>
     </row>
     <row r="26">
-      <c r="E26" s="10"/>
-      <c r="F26" s="11"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="13"/>
     </row>
     <row r="27">
-      <c r="E27" s="10"/>
-      <c r="F27" s="11"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="13"/>
     </row>
     <row r="28">
-      <c r="E28" s="10"/>
-      <c r="F28" s="11"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="13"/>
     </row>
     <row r="29">
-      <c r="E29" s="10"/>
-      <c r="F29" s="11"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="13"/>
     </row>
     <row r="30">
-      <c r="E30" s="10"/>
-      <c r="F30" s="11"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="13"/>
     </row>
     <row r="31">
-      <c r="E31" s="10"/>
-      <c r="F31" s="11"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="13"/>
     </row>
     <row r="32">
-      <c r="E32" s="10"/>
-      <c r="F32" s="11"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="13"/>
     </row>
     <row r="33">
-      <c r="E33" s="10"/>
-      <c r="F33" s="11"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="13"/>
     </row>
     <row r="34">
-      <c r="E34" s="10"/>
-      <c r="F34" s="11"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="13"/>
     </row>
     <row r="35">
-      <c r="E35" s="10"/>
-      <c r="F35" s="11"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="13"/>
     </row>
     <row r="36">
-      <c r="E36" s="10"/>
-      <c r="F36" s="11"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="13"/>
     </row>
     <row r="37">
-      <c r="E37" s="10"/>
-      <c r="F37" s="11"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="13"/>
     </row>
     <row r="38">
-      <c r="E38" s="10"/>
-      <c r="F38" s="11"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="13"/>
     </row>
     <row r="39">
-      <c r="E39" s="10"/>
-      <c r="F39" s="11"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="13"/>
     </row>
     <row r="40">
-      <c r="E40" s="10"/>
-      <c r="F40" s="11"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="13"/>
     </row>
     <row r="41">
-      <c r="E41" s="10"/>
-      <c r="F41" s="11"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="13"/>
     </row>
     <row r="42">
-      <c r="E42" s="10"/>
-      <c r="F42" s="11"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="13"/>
     </row>
     <row r="43">
-      <c r="E43" s="10"/>
-      <c r="F43" s="11"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="13"/>
     </row>
     <row r="44">
-      <c r="E44" s="10"/>
-      <c r="F44" s="11"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="13"/>
     </row>
     <row r="45">
-      <c r="E45" s="10"/>
-      <c r="F45" s="11"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="13"/>
     </row>
     <row r="46">
-      <c r="E46" s="10"/>
-      <c r="F46" s="11"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="13"/>
     </row>
     <row r="47">
-      <c r="E47" s="10"/>
-      <c r="F47" s="11"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="13"/>
     </row>
     <row r="48">
-      <c r="E48" s="10"/>
-      <c r="F48" s="11"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="13"/>
     </row>
     <row r="49">
-      <c r="E49" s="10"/>
-      <c r="F49" s="11"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="13"/>
     </row>
     <row r="50">
-      <c r="E50" s="10"/>
-      <c r="F50" s="11"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="13"/>
     </row>
     <row r="51">
-      <c r="E51" s="10"/>
-      <c r="F51" s="11"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="13"/>
     </row>
     <row r="52">
-      <c r="E52" s="10"/>
-      <c r="F52" s="11"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="13"/>
     </row>
     <row r="53">
-      <c r="E53" s="10"/>
-      <c r="F53" s="11"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="13"/>
     </row>
     <row r="54">
-      <c r="E54" s="10"/>
-      <c r="F54" s="11"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="13"/>
     </row>
     <row r="55">
-      <c r="E55" s="10"/>
-      <c r="F55" s="11"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="13"/>
     </row>
     <row r="56">
-      <c r="E56" s="10"/>
-      <c r="F56" s="11"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="13"/>
     </row>
     <row r="57">
-      <c r="E57" s="10"/>
-      <c r="F57" s="11"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="13"/>
     </row>
     <row r="58">
-      <c r="E58" s="10"/>
-      <c r="F58" s="11"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="13"/>
     </row>
     <row r="59">
-      <c r="E59" s="10"/>
-      <c r="F59" s="11"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="13"/>
     </row>
     <row r="60">
-      <c r="E60" s="10"/>
-      <c r="F60" s="11"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="13"/>
     </row>
     <row r="61">
-      <c r="E61" s="10"/>
-      <c r="F61" s="11"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="13"/>
     </row>
     <row r="62">
-      <c r="E62" s="10"/>
-      <c r="F62" s="11"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="13"/>
     </row>
     <row r="63">
-      <c r="E63" s="10"/>
-      <c r="F63" s="11"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="13"/>
     </row>
     <row r="64">
-      <c r="E64" s="10"/>
-      <c r="F64" s="11"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="13"/>
     </row>
     <row r="65">
-      <c r="E65" s="10"/>
-      <c r="F65" s="11"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="13"/>
     </row>
     <row r="66">
-      <c r="E66" s="10"/>
-      <c r="F66" s="11"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="13"/>
     </row>
     <row r="67">
-      <c r="E67" s="10"/>
-      <c r="F67" s="11"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="13"/>
     </row>
     <row r="68">
-      <c r="E68" s="10"/>
-      <c r="F68" s="11"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="13"/>
     </row>
     <row r="69">
-      <c r="E69" s="10"/>
-      <c r="F69" s="11"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="13"/>
     </row>
     <row r="70">
-      <c r="E70" s="10"/>
-      <c r="F70" s="11"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="13"/>
     </row>
     <row r="71">
-      <c r="E71" s="10"/>
-      <c r="F71" s="11"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="13"/>
     </row>
     <row r="72">
-      <c r="E72" s="10"/>
-      <c r="F72" s="11"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="13"/>
     </row>
     <row r="73">
-      <c r="E73" s="10"/>
-      <c r="F73" s="11"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="13"/>
     </row>
     <row r="74">
-      <c r="E74" s="10"/>
-      <c r="F74" s="11"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="13"/>
     </row>
     <row r="75">
-      <c r="E75" s="10"/>
-      <c r="F75" s="11"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="13"/>
     </row>
     <row r="76">
-      <c r="E76" s="10"/>
-      <c r="F76" s="11"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="13"/>
     </row>
     <row r="77">
-      <c r="E77" s="10"/>
-      <c r="F77" s="11"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="13"/>
     </row>
     <row r="78">
-      <c r="E78" s="10"/>
-      <c r="F78" s="11"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="13"/>
     </row>
     <row r="79">
-      <c r="E79" s="10"/>
-      <c r="F79" s="11"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="13"/>
     </row>
     <row r="80">
-      <c r="E80" s="10"/>
-      <c r="F80" s="11"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="13"/>
     </row>
     <row r="81">
-      <c r="E81" s="10"/>
-      <c r="F81" s="11"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="13"/>
     </row>
     <row r="82">
-      <c r="E82" s="10"/>
-      <c r="F82" s="11"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="13"/>
     </row>
     <row r="83">
-      <c r="E83" s="10"/>
-      <c r="F83" s="11"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="13"/>
     </row>
     <row r="84">
-      <c r="E84" s="10"/>
-      <c r="F84" s="11"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="13"/>
     </row>
     <row r="85">
-      <c r="E85" s="10"/>
-      <c r="F85" s="11"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="13"/>
     </row>
     <row r="86">
-      <c r="E86" s="10"/>
-      <c r="F86" s="11"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="13"/>
     </row>
     <row r="87">
-      <c r="E87" s="10"/>
-      <c r="F87" s="11"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="13"/>
     </row>
     <row r="88">
-      <c r="E88" s="10"/>
-      <c r="F88" s="11"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="13"/>
     </row>
     <row r="89">
-      <c r="E89" s="10"/>
-      <c r="F89" s="11"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="13"/>
     </row>
     <row r="90">
-      <c r="E90" s="10"/>
-      <c r="F90" s="11"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="13"/>
     </row>
     <row r="91">
-      <c r="E91" s="10"/>
-      <c r="F91" s="11"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="13"/>
     </row>
     <row r="92">
-      <c r="E92" s="10"/>
-      <c r="F92" s="11"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="13"/>
     </row>
     <row r="93">
-      <c r="E93" s="10"/>
-      <c r="F93" s="11"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="13"/>
     </row>
     <row r="94">
-      <c r="E94" s="10"/>
-      <c r="F94" s="11"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="13"/>
     </row>
     <row r="95">
-      <c r="E95" s="10"/>
-      <c r="F95" s="11"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="13"/>
     </row>
     <row r="96">
-      <c r="E96" s="10"/>
-      <c r="F96" s="11"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="13"/>
     </row>
     <row r="97">
-      <c r="E97" s="10"/>
-      <c r="F97" s="11"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="13"/>
     </row>
     <row r="98">
-      <c r="E98" s="10"/>
-      <c r="F98" s="11"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="13"/>
     </row>
     <row r="99">
-      <c r="E99" s="10"/>
-      <c r="F99" s="11"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="13"/>
     </row>
     <row r="100">
-      <c r="E100" s="10"/>
-      <c r="F100" s="11"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="13"/>
     </row>
     <row r="101">
-      <c r="E101" s="10"/>
-      <c r="F101" s="11"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="13"/>
     </row>
     <row r="102">
-      <c r="E102" s="10"/>
-      <c r="F102" s="11"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="13"/>
     </row>
     <row r="103">
-      <c r="E103" s="10"/>
-      <c r="F103" s="11"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="13"/>
     </row>
     <row r="104">
-      <c r="E104" s="10"/>
-      <c r="F104" s="11"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="13"/>
     </row>
     <row r="105">
-      <c r="E105" s="10"/>
-      <c r="F105" s="11"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="13"/>
     </row>
     <row r="106">
-      <c r="E106" s="10"/>
-      <c r="F106" s="11"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="13"/>
     </row>
     <row r="107">
-      <c r="E107" s="10"/>
-      <c r="F107" s="11"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="13"/>
+    </row>
+    <row r="108">
+      <c r="E108" s="12"/>
+      <c r="F108" s="13"/>
+    </row>
+    <row r="109">
+      <c r="E109" s="12"/>
+      <c r="F109" s="13"/>
+    </row>
+    <row r="110">
+      <c r="E110" s="12"/>
+      <c r="F110" s="13"/>
+    </row>
+    <row r="111">
+      <c r="E111" s="12"/>
+      <c r="F111" s="13"/>
+    </row>
+    <row r="112">
+      <c r="E112" s="12"/>
+      <c r="F112" s="13"/>
+    </row>
+    <row r="113">
+      <c r="E113" s="12"/>
+      <c r="F113" s="13"/>
+    </row>
+    <row r="114">
+      <c r="E114" s="12"/>
+      <c r="F114" s="13"/>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G7">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G14">
       <formula1>OR(TIMEVALUE(TEXT(G2, "hh:mm:ss"))=G2, AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F7">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F14">
       <formula1>OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E7"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E14"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="L4"/>
     <hyperlink r:id="rId2" ref="L6"/>
     <hyperlink r:id="rId3" ref="L7"/>
+    <hyperlink r:id="rId4" ref="L8"/>
+    <hyperlink r:id="rId5" ref="L10"/>
+    <hyperlink r:id="rId6" ref="L11"/>
+    <hyperlink r:id="rId7" ref="L12"/>
   </hyperlinks>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId8"/>
   <tableParts count="1">
-    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
+++ b/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="85">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -246,6 +246,36 @@
   </si>
   <si>
     <t xml:space="preserve">Fue retirado por cuadrilla de limpieza de playas de José Ignacio </t>
+  </si>
+  <si>
+    <t>-34.9175880, -54.8561750</t>
+  </si>
+  <si>
+    <t>Zapatos 41</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1tJSC3QCBPN_AL1ro6RuQ4U7GuXt6bn1a, https://drive.google.com/open?id=1vEdnkP6YGGgFoT28fzrmy9FPr_p4fcwm</t>
+  </si>
+  <si>
+    <t>Lluvia</t>
+  </si>
+  <si>
+    <t>Sector B</t>
+  </si>
+  <si>
+    <t>-34.9007730, -55.2523400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delphinus delphis </t>
+  </si>
+  <si>
+    <t>Medido en necropsia</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1vj94j2mW_X0hqu_xCSlffv6yzsHDS6CN, https://drive.google.com/open?id=190wDXV7o87VWybmPokqTW9tWpCSuG-Dz, https://drive.google.com/open?id=19SVZJ9u-5WXdW7AlZhSwn4dUZymkAqWL, https://drive.google.com/open?id=1rpqeNUPomYAUgIN07nGFqTQfEFCHoB9v, https://drive.google.com/open?id=1EDI4d3Jsrm8gV7td7xXoRs2P73B-k5T8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llevado a FacVeterinaria </t>
   </si>
 </sst>
 </file>
@@ -420,7 +450,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M14" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M16" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="13">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="Relevado por" id="2"/>
@@ -1222,20 +1252,94 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15">
-      <c r="E15" s="12"/>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16">
-      <c r="E16" s="14"/>
-      <c r="F16" s="13"/>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="4">
+        <v>46119.72220582176</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="7">
+        <v>46104.0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0.6944444444452529</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="4">
+        <v>46119.72955101852</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="7">
+        <v>46106.0</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0.5833333333357587</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="17">
       <c r="E17" s="12"/>
       <c r="F17" s="13"/>
     </row>
     <row r="18">
-      <c r="E18" s="12"/>
+      <c r="E18" s="14"/>
       <c r="F18" s="13"/>
     </row>
     <row r="19">
@@ -1622,15 +1726,23 @@
       <c r="E114" s="12"/>
       <c r="F114" s="13"/>
     </row>
+    <row r="115">
+      <c r="E115" s="12"/>
+      <c r="F115" s="13"/>
+    </row>
+    <row r="116">
+      <c r="E116" s="12"/>
+      <c r="F116" s="13"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G16">
       <formula1>OR(TIMEVALUE(TEXT(G2, "hh:mm:ss"))=G2, AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F14">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F16">
       <formula1>OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E14"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E16"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="L4"/>

--- a/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
+++ b/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="126">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -91,7 +91,17 @@
     <t>Marcador verde</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=10JR0Fam1_TrA47lL-0SlKqHit_CNqclk, https://drive.google.com/open?id=1ANLKItSbaZp4uDBMmXzXq24N42pUHwrJ</t>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://drive.google.com/open?id=10JR0Fam1_TrA47lL-0SlKqHit_CNqclk, </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://drive.google.com/open?id=1ANLKItSbaZp4uDBMmXzXq24N42pUHwrJ</t>
+    </r>
   </si>
   <si>
     <t>Viento sur</t>
@@ -276,6 +286,129 @@
   </si>
   <si>
     <t xml:space="preserve">Llevado a FacVeterinaria </t>
+  </si>
+  <si>
+    <t>Sector C</t>
+  </si>
+  <si>
+    <t>-34.8783120, -55.1052160</t>
+  </si>
+  <si>
+    <t>Pingüino Magallanes. Spheniscus magellanicus</t>
+  </si>
+  <si>
+    <t>Zpatilla 41</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1K85ZCbUf1pVDGfk4is2lw-z0DrQXRI3F, https://drive.google.com/open?id=1Kgr6MJp2kzklLpIVUk5zV_zKVPpbRwv7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hablé con 4 guardavidas </t>
+  </si>
+  <si>
+    <t>-34.8790620, -55.1171800</t>
+  </si>
+  <si>
+    <t>Sp reptil tortuga</t>
+  </si>
+  <si>
+    <t>Zapatilla 41</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1ep0pT-acVdmncJF01zQ1d5dpIyeG6RnX, https://drive.google.com/open?id=1BB-6KVic4c1Fk0Z4mtvn8lgSJxxJdLzf</t>
+  </si>
+  <si>
+    <t>Avisaron de 2 tortugas pero solo encontré una</t>
+  </si>
+  <si>
+    <t>-34.9217010, -54.8711750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cinta métrica </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1l6uDn6CkqrIBmwptZUuE39tnLA18sW0K, https://drive.google.com/open?id=1j75B3oQhGy_297iquxYkb7OdfbLirD41, https://drive.google.com/open?id=1-Fum78bQYiPGgIbOyC3tKuzBuWd7wa_Y, https://drive.google.com/open?id=1DyBCayBXSZLLBGixmobEi8cFww8X-qdH, https://drive.google.com/open?id=1qOzmqJFzoNnukYBSzo5bW1cL02theNwE</t>
+  </si>
+  <si>
+    <t>Dos marcas brasileñas en aletas anteriores</t>
+  </si>
+  <si>
+    <t>-34.8325270, -54.6272130</t>
+  </si>
+  <si>
+    <t>Spheniscus magellanicus</t>
+  </si>
+  <si>
+    <t>Calzado 41</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1HVO837WxBrH9v6envq6DCvRN25HJKckn</t>
+  </si>
+  <si>
+    <t>-34.8148850, -54.5952220</t>
+  </si>
+  <si>
+    <t>27/03/0026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pontoporia blainvillei </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Rs07DqDPbyPFAXjVZ95WHjTv9yM1iAFe, https://drive.google.com/open?id=1tLCm2zeTpsKtYlRizw5_UHiRaTvNL_Pk, https://drive.google.com/open?id=1Bs2KEaSq4I9TrqRoYc1A67T6wdpCR3Fg</t>
+  </si>
+  <si>
+    <t>Germán acompaña monitoreo</t>
+  </si>
+  <si>
+    <t>-34.8137870, -54.5929650</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1RqGHpjsxqJE5OWAMxz28nqFCHnMVujIQ, https://drive.google.com/open?id=15xfNg9I-ay--NTN227SFde3y1YXQ4H9K, https://drive.google.com/open?id=1mhAR_Np7Zz1VMm8duqJfZbBHWCRj_iUv</t>
+  </si>
+  <si>
+    <t>-34.8608590, -54.7238390</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1cfeIA0IV2NbYOQTVzZKuSIo85esOPPGo, https://drive.google.com/open?id=1pJkVQKWcmN5KNSiwQ3Z3FgDJ-mJlfuns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencia y mas fotos... ver con Germán que acompañó el monitoreo </t>
+  </si>
+  <si>
+    <t>-34.8826190, -54.7687230</t>
+  </si>
+  <si>
+    <t>Sin referencia. 90cm largo</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1N8A6M30ELFVNt2MCXazjvHW15PfxNqtu, https://drive.google.com/open?id=1_9ovju04qT8niSPtABYXPkodF99W2oq2, https://drive.google.com/open?id=1d6shsi6r9wDrIoG0_deCIQRz3_fDgSLs, https://drive.google.com/open?id=1Yxze2gcJhwm6uQO2a2Zdasf2MzPiwoXY, https://drive.google.com/open?id=1XCtbIUriYQ7l3UhadKP-U4lmk2dsG3jy</t>
+  </si>
+  <si>
+    <t>Viento sur. Caranchos y Buitres comiendolo</t>
+  </si>
+  <si>
+    <t>-34.8817150, -54.7668880</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1TqzeZHSHYFfBMlT-_YOA9UVcj9XzjMTY, https://drive.google.com/open?id=1A2RBeAbvPn4-JECf4YyOth7rAuy0W7n5</t>
+  </si>
+  <si>
+    <t>Sin aletas posteriores y sin cabeza</t>
+  </si>
+  <si>
+    <t>-34.8386260, -54.6528000</t>
+  </si>
+  <si>
+    <t>Ejemplar vivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spheniscus magellanicus </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1u3-ubgxLZR8e8aE9DySZtTrLj_XsMtyJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hay mas fotos de este animal </t>
   </si>
 </sst>
 </file>
@@ -306,12 +439,12 @@
     </font>
     <font>
       <u/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF434343"/>
       <name val="Roboto"/>
     </font>
     <font>
       <u/>
-      <color rgb="FF434343"/>
+      <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
   </fonts>
@@ -450,7 +583,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M16" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M26" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="13">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="Relevado por" id="2"/>
@@ -797,7 +930,7 @@
       <c r="K3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="9" t="s">
         <v>26</v>
       </c>
       <c r="M3" s="5" t="s">
@@ -838,7 +971,7 @@
       <c r="K4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="10" t="s">
         <v>31</v>
       </c>
       <c r="M4" s="5" t="s">
@@ -920,7 +1053,7 @@
       <c r="K6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="11" t="s">
         <v>40</v>
       </c>
       <c r="M6" s="5" t="s">
@@ -961,7 +1094,7 @@
       <c r="K7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="11" t="s">
         <v>44</v>
       </c>
       <c r="M7" s="5" t="s">
@@ -1002,7 +1135,7 @@
       <c r="K8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="11" t="s">
         <v>49</v>
       </c>
       <c r="M8" s="5" t="s">
@@ -1084,7 +1217,7 @@
       <c r="K10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="9" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1122,7 +1255,7 @@
       <c r="K11" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="10" t="s">
         <v>61</v>
       </c>
       <c r="M11" s="5" t="s">
@@ -1163,7 +1296,7 @@
       <c r="K12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="11" t="s">
         <v>65</v>
       </c>
       <c r="M12" s="5" t="s">
@@ -1334,52 +1467,419 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17">
-      <c r="E17" s="12"/>
-      <c r="F17" s="13"/>
-    </row>
-    <row r="18">
-      <c r="E18" s="14"/>
-      <c r="F18" s="13"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="12"/>
-      <c r="F19" s="13"/>
-    </row>
-    <row r="20">
-      <c r="E20" s="12"/>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21">
-      <c r="E21" s="12"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22">
-      <c r="E22" s="12"/>
-      <c r="F22" s="13"/>
-    </row>
-    <row r="23">
-      <c r="E23" s="12"/>
-      <c r="F23" s="13"/>
-    </row>
-    <row r="24">
-      <c r="E24" s="12"/>
-      <c r="F24" s="13"/>
-    </row>
-    <row r="25">
-      <c r="E25" s="12"/>
-      <c r="F25" s="13"/>
-    </row>
-    <row r="26">
-      <c r="E26" s="12"/>
-      <c r="F26" s="13"/>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="4">
+        <v>46120.67501521991</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="7">
+        <v>46107.0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0.45277777777664596</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="4">
+        <v>46120.680448900464</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="7">
+        <v>46107.0</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0.43402777778101154</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="4">
+        <v>46120.68625732639</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="7">
+        <v>46107.0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0.5833333333357587</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="4">
+        <v>46120.6937684838</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="7">
+        <v>46108.0</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0.38541666666424135</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1">
+      <c r="A21" s="4">
+        <v>46120.699353414355</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0.024305555554747116</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="4">
+        <v>46120.70533869213</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" s="7">
+        <v>46108.0</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0.027777777781011537</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="A23" s="4">
+        <v>46120.715158657404</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="7">
+        <v>46109.0</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0.42708333333575865</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="A24" s="4">
+        <v>46120.72699841435</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" s="7">
+        <v>46116.0</v>
+      </c>
+      <c r="G24" s="8">
+        <v>0.47222222221898846</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="A25" s="4">
+        <v>46120.72945604166</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="7">
+        <v>46116.0</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0.47916666666424135</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" ht="22.5" customHeight="1">
+      <c r="A26" s="4">
+        <v>46120.734293981484</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F26" s="7">
+        <v>46116.0</v>
+      </c>
+      <c r="G26" s="8">
+        <v>0.5277777777777778</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I26" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="27">
       <c r="E27" s="12"/>
       <c r="F27" s="13"/>
     </row>
     <row r="28">
-      <c r="E28" s="12"/>
+      <c r="E28" s="14"/>
       <c r="F28" s="13"/>
     </row>
     <row r="29">
@@ -1734,28 +2234,71 @@
       <c r="E116" s="12"/>
       <c r="F116" s="13"/>
     </row>
+    <row r="117">
+      <c r="E117" s="12"/>
+      <c r="F117" s="13"/>
+    </row>
+    <row r="118">
+      <c r="E118" s="12"/>
+      <c r="F118" s="13"/>
+    </row>
+    <row r="119">
+      <c r="E119" s="12"/>
+      <c r="F119" s="13"/>
+    </row>
+    <row r="120">
+      <c r="E120" s="12"/>
+      <c r="F120" s="13"/>
+    </row>
+    <row r="121">
+      <c r="E121" s="12"/>
+      <c r="F121" s="13"/>
+    </row>
+    <row r="122">
+      <c r="E122" s="12"/>
+      <c r="F122" s="13"/>
+    </row>
+    <row r="123">
+      <c r="E123" s="12"/>
+      <c r="F123" s="13"/>
+    </row>
+    <row r="124">
+      <c r="E124" s="12"/>
+      <c r="F124" s="13"/>
+    </row>
+    <row r="125">
+      <c r="E125" s="12"/>
+      <c r="F125" s="13"/>
+    </row>
+    <row r="126">
+      <c r="E126" s="12"/>
+      <c r="F126" s="13"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G16">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G26">
       <formula1>OR(TIMEVALUE(TEXT(G2, "hh:mm:ss"))=G2, AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F16">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F26">
       <formula1>OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E16"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E26"/>
   </dataValidations>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="L4"/>
-    <hyperlink r:id="rId2" ref="L6"/>
-    <hyperlink r:id="rId3" ref="L7"/>
-    <hyperlink r:id="rId4" ref="L8"/>
-    <hyperlink r:id="rId5" ref="L10"/>
-    <hyperlink r:id="rId6" ref="L11"/>
-    <hyperlink r:id="rId7" ref="L12"/>
+    <hyperlink r:id="rId1" ref="L3"/>
+    <hyperlink r:id="rId2" ref="L4"/>
+    <hyperlink r:id="rId3" ref="L6"/>
+    <hyperlink r:id="rId4" ref="L7"/>
+    <hyperlink r:id="rId5" ref="L8"/>
+    <hyperlink r:id="rId6" ref="L10"/>
+    <hyperlink r:id="rId7" ref="L11"/>
+    <hyperlink r:id="rId8" ref="L12"/>
+    <hyperlink r:id="rId9" ref="L20"/>
+    <hyperlink r:id="rId10" ref="L26"/>
   </hyperlinks>
-  <drawing r:id="rId8"/>
+  <drawing r:id="rId11"/>
   <tableParts count="1">
-    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId13"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
+++ b/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="136">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -409,6 +409,37 @@
   </si>
   <si>
     <t xml:space="preserve">Hay mas fotos de este animal </t>
+  </si>
+  <si>
+    <t>-34.9646819, -54.9401965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A definir </t>
+  </si>
+  <si>
+    <t>Cinta métrica  y marcador verde</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1j1Se8aV8StvYK2ESZRUbOW5fVZT-zZ0L, https://drive.google.com/open?id=1WY2uQuN8NX_E-F-iC06oyjLyt_OfMJRQ, https://drive.google.com/open?id=1siYaptZQ-9Q7A28uyXoqmjEg6De11chh, https://drive.google.com/open?id=1iC5Dnc71mko5S3ZOQj0od9GOaAxddXok</t>
+  </si>
+  <si>
+    <t>Post tormenta de tres dias.
+Tres individuos juntos</t>
+  </si>
+  <si>
+    <t>-34.9643080, -54.9407140</t>
+  </si>
+  <si>
+    <t>Pardwla cabeza negra a confirmar</t>
+  </si>
+  <si>
+    <t>Cinta metrica y marcador verde</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1avbOfB5MsFu4pFFKelKsiszFXz1olsPk, https://drive.google.com/open?id=1UuqNgraSED4hoaVhzqzjhEoT41PiNkow</t>
+  </si>
+  <si>
+    <t>Misma región de las otras 3</t>
   </si>
 </sst>
 </file>
@@ -583,7 +614,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M26" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M28" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="13">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="Relevado por" id="2"/>
@@ -1874,20 +1905,94 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27">
-      <c r="E27" s="12"/>
-      <c r="F27" s="13"/>
-    </row>
-    <row r="28">
-      <c r="E28" s="14"/>
-      <c r="F28" s="13"/>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="4">
+        <v>46122.32079516204</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" s="7">
+        <v>46122.0</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0.3125</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" ht="22.5" customHeight="1">
+      <c r="A28" s="4">
+        <v>46122.32875987269</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F28" s="7">
+        <v>46122.0</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0.3243055555576575</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="29">
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
     </row>
     <row r="30">
-      <c r="E30" s="12"/>
+      <c r="E30" s="14"/>
       <c r="F30" s="13"/>
     </row>
     <row r="31">
@@ -2274,15 +2379,23 @@
       <c r="E126" s="12"/>
       <c r="F126" s="13"/>
     </row>
+    <row r="127">
+      <c r="E127" s="12"/>
+      <c r="F127" s="13"/>
+    </row>
+    <row r="128">
+      <c r="E128" s="12"/>
+      <c r="F128" s="13"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G26">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G28">
       <formula1>OR(TIMEVALUE(TEXT(G2, "hh:mm:ss"))=G2, AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F26">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F28">
       <formula1>OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E26"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E28"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="L3"/>

--- a/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
+++ b/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="144">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -440,6 +440,30 @@
   </si>
   <si>
     <t>Misma región de las otras 3</t>
+  </si>
+  <si>
+    <t>-34.6844420, -54.2801900</t>
+  </si>
+  <si>
+    <t>Spheniscus magellanicus??</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1lwbPcOFkts-I56q7eJvHIXqghVNnFKcK, https://drive.google.com/open?id=1H2FAq0BG7ig1sDpSWvnor4sPlxwJHi96</t>
+  </si>
+  <si>
+    <t>-34.6823070, -54.2719480</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1slRqh_2ztL1Zu1eI8lLjuNjg4WXzKC6R</t>
+  </si>
+  <si>
+    <t>Barra de la laguna cerrada</t>
+  </si>
+  <si>
+    <t>-34.6863650, -54.2871040</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1uKDrW7CH7EEQcH_HoOKzCjTxoEDEgLCa, https://drive.google.com/open?id=1fXUx_dwyO22RL27sVPZ4MrmILFGfsdSg, https://drive.google.com/open?id=17Wtj2sjggpotCxXgBaPTAWHrpnZrKJxh</t>
   </si>
 </sst>
 </file>
@@ -614,7 +638,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M28" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M31" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="13">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="Relevado por" id="2"/>
@@ -1987,24 +2011,135 @@
         <v>135</v>
       </c>
     </row>
-    <row r="29">
-      <c r="E29" s="12"/>
-      <c r="F29" s="13"/>
-    </row>
-    <row r="30">
-      <c r="E30" s="14"/>
-      <c r="F30" s="13"/>
-    </row>
-    <row r="31">
-      <c r="E31" s="12"/>
-      <c r="F31" s="13"/>
+    <row r="29" ht="22.5" customHeight="1">
+      <c r="A29" s="4">
+        <v>46123.46916921296</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F29" s="7">
+        <v>46123.0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0.4618055555547471</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" customHeight="1">
+      <c r="A30" s="4">
+        <v>46123.48425252315</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="7">
+        <v>46123.0</v>
+      </c>
+      <c r="G30" s="8">
+        <v>0.47916666666424135</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" customHeight="1">
+      <c r="A31" s="4">
+        <v>46123.804178252314</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" s="7">
+        <v>46123.0</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0.4930555555547471</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="32">
       <c r="E32" s="12"/>
       <c r="F32" s="13"/>
     </row>
     <row r="33">
-      <c r="E33" s="12"/>
+      <c r="E33" s="14"/>
       <c r="F33" s="13"/>
     </row>
     <row r="34">
@@ -2387,15 +2522,27 @@
       <c r="E128" s="12"/>
       <c r="F128" s="13"/>
     </row>
+    <row r="129">
+      <c r="E129" s="12"/>
+      <c r="F129" s="13"/>
+    </row>
+    <row r="130">
+      <c r="E130" s="12"/>
+      <c r="F130" s="13"/>
+    </row>
+    <row r="131">
+      <c r="E131" s="12"/>
+      <c r="F131" s="13"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G28">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G31">
       <formula1>OR(TIMEVALUE(TEXT(G2, "hh:mm:ss"))=G2, AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F28">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F31">
       <formula1>OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E28"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E31"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="L3"/>
@@ -2408,10 +2555,11 @@
     <hyperlink r:id="rId8" ref="L12"/>
     <hyperlink r:id="rId9" ref="L20"/>
     <hyperlink r:id="rId10" ref="L26"/>
+    <hyperlink r:id="rId11" ref="L30"/>
   </hyperlinks>
-  <drawing r:id="rId11"/>
+  <drawing r:id="rId12"/>
   <tableParts count="1">
-    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId14"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
+++ b/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="153">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -464,6 +464,33 @@
   </si>
   <si>
     <t>https://drive.google.com/open?id=1uKDrW7CH7EEQcH_HoOKzCjTxoEDEgLCa, https://drive.google.com/open?id=1fXUx_dwyO22RL27sVPZ4MrmILFGfsdSg, https://drive.google.com/open?id=17Wtj2sjggpotCxXgBaPTAWHrpnZrKJxh</t>
+  </si>
+  <si>
+    <t>-34.8421701, -54.6732507</t>
+  </si>
+  <si>
+    <t>A definir</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=12wQn7d3TzBXVHUj5h8vBOROh2u-fIqeM</t>
+  </si>
+  <si>
+    <t>Barra cerrada</t>
+  </si>
+  <si>
+    <t>-34.8432910, -54.6748540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pardela Cabeza Negra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcador verde </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1SYbhf8s9k3gteYGJRGSdqRGYrWxpYrJN, https://drive.google.com/open?id=1E0tgxgs2tHwVT4m_vBertUFwkGdyO3G4</t>
+  </si>
+  <si>
+    <t>Marea subiendo</t>
   </si>
 </sst>
 </file>
@@ -638,7 +665,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M31" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M33" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="13">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="Relevado por" id="2"/>
@@ -2134,20 +2161,94 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32">
-      <c r="E32" s="12"/>
-      <c r="F32" s="13"/>
-    </row>
-    <row r="33">
-      <c r="E33" s="14"/>
-      <c r="F33" s="13"/>
+    <row r="32" ht="22.5" customHeight="1">
+      <c r="A32" s="4">
+        <v>46124.481261469904</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F32" s="7">
+        <v>46124.0</v>
+      </c>
+      <c r="G32" s="8">
+        <v>0.4756944444452529</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" customHeight="1">
+      <c r="A33" s="4">
+        <v>46124.489053136575</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F33" s="7">
+        <v>46124.0</v>
+      </c>
+      <c r="G33" s="8">
+        <v>0.48611111110949423</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I33" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="34">
       <c r="E34" s="12"/>
       <c r="F34" s="13"/>
     </row>
     <row r="35">
-      <c r="E35" s="12"/>
+      <c r="E35" s="14"/>
       <c r="F35" s="13"/>
     </row>
     <row r="36">
@@ -2534,15 +2635,23 @@
       <c r="E131" s="12"/>
       <c r="F131" s="13"/>
     </row>
+    <row r="132">
+      <c r="E132" s="12"/>
+      <c r="F132" s="13"/>
+    </row>
+    <row r="133">
+      <c r="E133" s="12"/>
+      <c r="F133" s="13"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G31">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G33">
       <formula1>OR(TIMEVALUE(TEXT(G2, "hh:mm:ss"))=G2, AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F31">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F33">
       <formula1>OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E31"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E33"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="L3"/>
@@ -2556,10 +2665,11 @@
     <hyperlink r:id="rId9" ref="L20"/>
     <hyperlink r:id="rId10" ref="L26"/>
     <hyperlink r:id="rId11" ref="L30"/>
+    <hyperlink r:id="rId12" ref="L32"/>
   </hyperlinks>
-  <drawing r:id="rId12"/>
+  <drawing r:id="rId13"/>
   <tableParts count="1">
-    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
+++ b/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="159">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -491,6 +491,24 @@
   </si>
   <si>
     <t>Marea subiendo</t>
+  </si>
+  <si>
+    <t>Sector A</t>
+  </si>
+  <si>
+    <t>-34.7894050, -55.3965500</t>
+  </si>
+  <si>
+    <t>Ave sp</t>
+  </si>
+  <si>
+    <t>Regla del monitoreo</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1IDtoetcW2KpFB8N9HQ-7Uy103LbyfSn6, https://drive.google.com/open?id=1LH56mlfsfPBiQZRXvHUgYIz1rrTLg8gV, https://drive.google.com/open?id=1KBm8PymYdb11w9nZ87YV_9StUt9YyL74, https://drive.google.com/open?id=1WoR9XWxiJOMmiH8_4olwKGIbpaOArsjB</t>
+  </si>
+  <si>
+    <t>Viento del noroeste</t>
   </si>
 </sst>
 </file>
@@ -665,7 +683,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M33" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M34" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="13">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="Relevado por" id="2"/>
@@ -2243,16 +2261,53 @@
         <v>152</v>
       </c>
     </row>
-    <row r="34">
-      <c r="E34" s="12"/>
-      <c r="F34" s="13"/>
+    <row r="34" ht="22.5" customHeight="1">
+      <c r="A34" s="4">
+        <v>46131.52780790509</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F34" s="7">
+        <v>46131.0</v>
+      </c>
+      <c r="G34" s="8">
+        <v>0.44791666666424135</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="35">
-      <c r="E35" s="14"/>
+      <c r="E35" s="12"/>
       <c r="F35" s="13"/>
     </row>
     <row r="36">
-      <c r="E36" s="12"/>
+      <c r="E36" s="14"/>
       <c r="F36" s="13"/>
     </row>
     <row r="37">
@@ -2643,15 +2698,19 @@
       <c r="E133" s="12"/>
       <c r="F133" s="13"/>
     </row>
+    <row r="134">
+      <c r="E134" s="12"/>
+      <c r="F134" s="13"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G33">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G34">
       <formula1>OR(TIMEVALUE(TEXT(G2, "hh:mm:ss"))=G2, AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F33">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F34">
       <formula1>OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E33"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E34"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="L3"/>

--- a/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
+++ b/Respaldo_PMPUy/Formulario (no editar manualmente)/Registro de varamientos.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="164">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -509,6 +509,21 @@
   </si>
   <si>
     <t>Viento del noroeste</t>
+  </si>
+  <si>
+    <t>-34.9122320, -54.8419470</t>
+  </si>
+  <si>
+    <t>Pinnípedo sp</t>
+  </si>
+  <si>
+    <t>Regla GTV</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1-EL0KMFbAQ4RIeGFwfM2oA3rI8byICBI, https://drive.google.com/open?id=14QUNcSUZGCQ-jLbO8ie96Fxx_Z510IvZ, https://drive.google.com/open?id=1XLtPUAMrVmzEiXSuSXgh5X1xVZHLEroZ, https://drive.google.com/open?id=1uouRw4AEEzWN3r23lOn5_H1du-48dnaH</t>
+  </si>
+  <si>
+    <t>Nublado, llovizna y viento suave sureste</t>
   </si>
 </sst>
 </file>
@@ -683,7 +698,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M34" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M35" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="13">
     <tableColumn name="Marca temporal" id="1"/>
     <tableColumn name="Relevado por" id="2"/>
@@ -2302,16 +2317,53 @@
         <v>158</v>
       </c>
     </row>
-    <row r="35">
-      <c r="E35" s="12"/>
-      <c r="F35" s="13"/>
+    <row r="35" ht="22.5" customHeight="1">
+      <c r="A35" s="4">
+        <v>46132.55771586805</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F35" s="7">
+        <v>46132.0</v>
+      </c>
+      <c r="G35" s="8">
+        <v>0.3680555555547471</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="36">
-      <c r="E36" s="14"/>
+      <c r="E36" s="12"/>
       <c r="F36" s="13"/>
     </row>
     <row r="37">
-      <c r="E37" s="12"/>
+      <c r="E37" s="14"/>
       <c r="F37" s="13"/>
     </row>
     <row r="38">
@@ -2702,15 +2754,19 @@
       <c r="E134" s="12"/>
       <c r="F134" s="13"/>
     </row>
+    <row r="135">
+      <c r="E135" s="12"/>
+      <c r="F135" s="13"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G34">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2:G35">
       <formula1>OR(TIMEVALUE(TEXT(G2, "hh:mm:ss"))=G2, AND(ISNUMBER(G2), LEFT(CELL("format", G2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F34">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F35">
       <formula1>OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D"))</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E34"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="E2:E35"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="L3"/>
